--- a/output/pdf_financials_xlsx/ROOT.xlsx
+++ b/output/pdf_financials_xlsx/ROOT.xlsx
@@ -1832,10 +1832,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.991</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1848,19 +1848,19 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>34.161</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>31.921</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>28.033</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>34.021</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>28.633</v>
       </c>
     </row>
     <row r="35">
@@ -1914,10 +1914,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.991</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1930,19 +1930,19 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>34.161</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>31.921</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>28.033</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>34.021</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>28.633</v>
       </c>
     </row>
     <row r="37">
@@ -2406,10 +2406,10 @@
         <v>26.31</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.848</v>
+        <v>5.039</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.238</v>
+        <v>6.247</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -2422,19 +2422,19 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>38.9</v>
+        <v>4.739</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>35.481</v>
+        <v>3.56</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>33.559</v>
+        <v>5.526</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>39.937</v>
+        <v>5.916</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>31.705</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="49">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>-19.654</v>
+        <v>-19.857</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>-4.984</v>
+        <v>-5.345</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>-4.984</v>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-19.654</v>
+        <v>-19.857</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-4.984</v>
+        <v>-5.345</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>-4.984</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -19946,11 +19946,7 @@
           <t>Amortization of lease intangibles 7</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -20534,7 +20530,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -21244,11 +21244,7 @@
           <t>Amortization of lease intangibles (Note 6)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ROOT.xlsx
+++ b/output/pdf_financials_xlsx/ROOT.xlsx
@@ -15820,7 +15820,11 @@
           <t>Additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
